--- a/Análisis_de_Datos_con_Excel.xlsx
+++ b/Análisis_de_Datos_con_Excel.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Escritorio\Repositorio_Análisis_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F0D070-5FC5-4822-9F2A-DDF748D381EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F260297D-2624-433B-8376-363CB82B6AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-1290" windowWidth="20730" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-1290" windowWidth="20730" windowHeight="11760" tabRatio="500" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sobre este análisis" sheetId="1" r:id="rId1"/>
-    <sheet name="Datos_Crudos" sheetId="2" r:id="rId2"/>
-    <sheet name="Data Profiling" sheetId="9" r:id="rId3"/>
+    <sheet name="Data Profiling" sheetId="9" r:id="rId2"/>
+    <sheet name="Datos_Crudos" sheetId="2" r:id="rId3"/>
     <sheet name="Datos_Limpios" sheetId="3" r:id="rId4"/>
     <sheet name="Preguntas" sheetId="4" r:id="rId5"/>
     <sheet name="Evidencia Respuestas" sheetId="10" r:id="rId6"/>
@@ -3983,14 +3983,6 @@
     <t>Promedio de Purchase_Amount</t>
   </si>
   <si>
-    <t>Sri Lanka: $10.239,39
-Afghanistan: $10.194,42
-Pakistan: $10.133,48
-India: $9.702,71
-Nepal: $9.673,68
-Bangladesh: 9.361,83</t>
-  </si>
-  <si>
     <t>Clothing: $955.529</t>
   </si>
   <si>
@@ -4088,16 +4080,10 @@
     <t>dic</t>
   </si>
   <si>
-    <t>Evolución de compras mensuales (2022-2025)</t>
-  </si>
-  <si>
     <t>Monto total de compras por país</t>
   </si>
   <si>
     <t>Sobre este Análisis</t>
-  </si>
-  <si>
-    <t>Analicé un dataset de 515 clientes de una tienda online que opera en el sur de Asia (Afganistán, Bangladesh, India, Nepal, Pakistán y Sri Lanka), con el objetivo de identificar patrones de compra por país, categoría de producto y periodo de tiempo, y proponer recomendaciones de negocio basadas en los hallazgos.</t>
   </si>
   <si>
     <t>Proceso</t>
@@ -4167,21 +4153,6 @@
   </si>
   <si>
     <r>
-      <t>5. Conclusiones:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> cerré el análisis con hallazgos clave y una recomendación de negocio.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Herramientas usadas:</t>
     </r>
     <r>
@@ -4322,19 +4293,10 @@
     <t>10 valores vacíos; algunos negativos</t>
   </si>
   <si>
-    <t>Vacíos eliminados; negativos convertidos a valor absoluto</t>
-  </si>
-  <si>
     <t>Normalizado</t>
   </si>
   <si>
     <t>14 valores vacíos</t>
-  </si>
-  <si>
-    <t>15 filas completas duplicadas</t>
-  </si>
-  <si>
-    <t>Eliminadas</t>
   </si>
   <si>
     <t>Pakistan: 89
@@ -4352,18 +4314,6 @@
   </si>
   <si>
     <t>1. Con 484 clientes válidos tras la limpieza, se registraron $4.786.627 en compras totales.</t>
-  </si>
-  <si>
-    <t>2. Pakistán lidera tanto en cantidad de clientes (89) como en monto total de compras ($901,880) — es el mercado más fuerte.</t>
-  </si>
-  <si>
-    <t>3. Clothing es la categoría con mayor monto de compras ($955,529), pero presenta una paradoja: tiene uno de los ratings promedio más bajos (2.84). Furniture, en cambio, tiene el mejor rating (3.21) pese a tener un menor monto de compras.</t>
-  </si>
-  <si>
-    <t>4. 2023 y 2024 fueron los años con mayor monto de compras (~$1.5M cada uno); 2025 muestra cifras menores, pero esto es engañoso, ya que los datos de ese año solo cubren hasta mayo.</t>
-  </si>
-  <si>
-    <t>5. La distribución de clientes por género es exactamente equilibrada (242 hombres, 242 mujeres) — no hay sesgo de género en la base de clientes.</t>
   </si>
   <si>
     <r>
@@ -4400,6 +4350,56 @@
       </rPr>
       <t xml:space="preserve"> — diagnóstico de calidad de datos por columna</t>
     </r>
+  </si>
+  <si>
+    <t>Monto de compras por fecha de ingreso</t>
+  </si>
+  <si>
+    <t>5. La base de clientes está exactamente dividida por género (242 hombres y 242 mujeres). Este reparto tan exacto, junto con algunos nombres que no coinciden con el género registrado, sugiere que el dataset es sintético, así que conviene interpretar los hallazgos con cautela.</t>
+  </si>
+  <si>
+    <r>
+      <t>5. Conclusiones:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> cerré el análisis con hallazgos clave.</t>
+    </r>
+  </si>
+  <si>
+    <t>Vacíos eliminados; 22 negativos convertidos a valor absoluto, asumiendo error de digitación (el dataset no indica reembolsos).</t>
+  </si>
+  <si>
+    <t>Eliminados tras normalizar el texto y las fechas</t>
+  </si>
+  <si>
+    <t>Analicé un dataset de 515 registros de una tienda online que opera en el sur de Asia (Afganistán, Bangladesh, India, Nepal, Pakistán y Sri Lanka), con el objetivo de identificar patrones de compra por país, categoría de producto y periodo de tiempo.</t>
+  </si>
+  <si>
+    <t>Sri Lanka: $10.239,39
+Afghanistan: $10.194,42
+Pakistan: $10.133,48
+India: $9.702,71
+Nepal: $9.673,68
+Bangladesh: $9.361,83</t>
+  </si>
+  <si>
+    <t>2. Pakistán lidera tanto en cantidad de clientes (89) como en monto total de compras ($901.880) — es el mercado más fuerte.</t>
+  </si>
+  <si>
+    <t>15 IDs repetidos (mismo cliente registrado dos veces, con diferencias de formato en texto y fechas)</t>
+  </si>
+  <si>
+    <t>3. Clothing es la categoría con mayor monto de compras ($955.529), pero su rating promedio (2,84) está entre los más bajos. Los ratings de todas las categorías son similares (2,80 a 3,21), así que la diferencia es pequeña. Furniture tiene el rating más alto (3,21) con menor facturación.</t>
+  </si>
+  <si>
+    <t>4. Los clientes que se unieron en 2023 y 2024 suman montos casi iguales ($1,5M cada año). 2022 y 2025 son años incompletos y no se pueden comparar. El dataset no tiene fecha de compra, por eso el análisis usa la fecha de ingreso del cliente.</t>
   </si>
 </sst>
 </file>
@@ -4804,7 +4804,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4822,6 +4821,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4838,9 +4840,6 @@
       <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
     </dxf>
     <dxf>
@@ -4848,6 +4847,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -5865,9 +5867,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Compras totales por mes</a:t>
+              <a:rPr lang="es-CO" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Monto de compras por fecha de ingreso</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -20952,6 +20955,1130 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEB42CE3-9D07-47B6-A5DF-68C03766D442}" name="6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Country">
+  <location ref="D15:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="43">
+        <item x="13"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="39"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="2"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="40"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="38"/>
+        <item x="21"/>
+        <item x="27"/>
+        <item x="15"/>
+        <item x="25"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="41"/>
+        <item x="31"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="3"/>
+        <item x="22"/>
+        <item x="12"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="18"/>
+        <item x="1"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="30"/>
+        <item x="9"/>
+        <item x="23"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="29"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="406">
+        <item x="2"/>
+        <item x="132"/>
+        <item x="166"/>
+        <item x="189"/>
+        <item x="307"/>
+        <item x="44"/>
+        <item x="234"/>
+        <item x="360"/>
+        <item x="145"/>
+        <item x="289"/>
+        <item x="258"/>
+        <item x="380"/>
+        <item x="74"/>
+        <item x="334"/>
+        <item x="213"/>
+        <item x="382"/>
+        <item x="255"/>
+        <item x="142"/>
+        <item x="232"/>
+        <item x="92"/>
+        <item x="14"/>
+        <item x="46"/>
+        <item x="353"/>
+        <item x="243"/>
+        <item x="67"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="203"/>
+        <item x="208"/>
+        <item x="314"/>
+        <item x="17"/>
+        <item x="309"/>
+        <item x="272"/>
+        <item x="199"/>
+        <item x="349"/>
+        <item x="183"/>
+        <item x="96"/>
+        <item x="393"/>
+        <item x="346"/>
+        <item x="372"/>
+        <item x="268"/>
+        <item x="212"/>
+        <item x="111"/>
+        <item x="230"/>
+        <item x="221"/>
+        <item x="206"/>
+        <item x="336"/>
+        <item x="202"/>
+        <item x="269"/>
+        <item x="388"/>
+        <item x="238"/>
+        <item x="53"/>
+        <item x="254"/>
+        <item x="316"/>
+        <item x="319"/>
+        <item x="220"/>
+        <item x="200"/>
+        <item x="159"/>
+        <item x="216"/>
+        <item x="117"/>
+        <item x="352"/>
+        <item x="315"/>
+        <item x="292"/>
+        <item x="156"/>
+        <item x="261"/>
+        <item x="190"/>
+        <item x="113"/>
+        <item x="280"/>
+        <item x="146"/>
+        <item x="150"/>
+        <item x="172"/>
+        <item x="12"/>
+        <item x="19"/>
+        <item x="366"/>
+        <item x="262"/>
+        <item x="223"/>
+        <item x="52"/>
+        <item x="347"/>
+        <item x="81"/>
+        <item x="68"/>
+        <item x="402"/>
+        <item x="37"/>
+        <item x="305"/>
+        <item x="36"/>
+        <item x="395"/>
+        <item x="368"/>
+        <item x="77"/>
+        <item x="98"/>
+        <item x="171"/>
+        <item x="135"/>
+        <item x="400"/>
+        <item x="267"/>
+        <item x="217"/>
+        <item x="110"/>
+        <item x="134"/>
+        <item x="196"/>
+        <item x="298"/>
+        <item x="335"/>
+        <item x="185"/>
+        <item x="373"/>
+        <item x="55"/>
+        <item x="103"/>
+        <item x="351"/>
+        <item x="28"/>
+        <item x="50"/>
+        <item x="359"/>
+        <item x="327"/>
+        <item x="153"/>
+        <item x="181"/>
+        <item x="286"/>
+        <item x="401"/>
+        <item x="123"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="182"/>
+        <item x="204"/>
+        <item x="80"/>
+        <item x="4"/>
+        <item x="69"/>
+        <item x="143"/>
+        <item x="279"/>
+        <item x="186"/>
+        <item x="364"/>
+        <item x="301"/>
+        <item x="376"/>
+        <item x="342"/>
+        <item x="195"/>
+        <item x="148"/>
+        <item x="10"/>
+        <item x="320"/>
+        <item x="83"/>
+        <item x="235"/>
+        <item x="79"/>
+        <item x="251"/>
+        <item x="394"/>
+        <item x="332"/>
+        <item x="137"/>
+        <item x="259"/>
+        <item x="118"/>
+        <item x="99"/>
+        <item x="141"/>
+        <item x="188"/>
+        <item x="101"/>
+        <item x="398"/>
+        <item x="392"/>
+        <item x="356"/>
+        <item x="58"/>
+        <item x="180"/>
+        <item x="82"/>
+        <item x="211"/>
+        <item x="282"/>
+        <item x="3"/>
+        <item x="275"/>
+        <item x="225"/>
+        <item x="252"/>
+        <item x="355"/>
+        <item x="297"/>
+        <item x="283"/>
+        <item x="27"/>
+        <item x="354"/>
+        <item x="90"/>
+        <item x="371"/>
+        <item x="384"/>
+        <item x="168"/>
+        <item x="66"/>
+        <item x="341"/>
+        <item x="362"/>
+        <item x="129"/>
+        <item x="30"/>
+        <item x="294"/>
+        <item x="6"/>
+        <item x="115"/>
+        <item x="218"/>
+        <item x="105"/>
+        <item x="163"/>
+        <item x="224"/>
+        <item x="125"/>
+        <item x="328"/>
+        <item x="207"/>
+        <item x="120"/>
+        <item x="397"/>
+        <item x="21"/>
+        <item x="264"/>
+        <item x="333"/>
+        <item x="236"/>
+        <item x="300"/>
+        <item x="198"/>
+        <item x="226"/>
+        <item x="348"/>
+        <item x="383"/>
+        <item x="324"/>
+        <item x="385"/>
+        <item x="290"/>
+        <item x="144"/>
+        <item x="121"/>
+        <item x="62"/>
+        <item x="140"/>
+        <item x="215"/>
+        <item x="367"/>
+        <item x="122"/>
+        <item x="219"/>
+        <item x="178"/>
+        <item x="170"/>
+        <item x="13"/>
+        <item x="47"/>
+        <item x="194"/>
+        <item x="152"/>
+        <item x="95"/>
+        <item x="187"/>
+        <item x="158"/>
+        <item x="248"/>
+        <item x="242"/>
+        <item x="184"/>
+        <item x="296"/>
+        <item x="127"/>
+        <item x="114"/>
+        <item x="116"/>
+        <item x="237"/>
+        <item x="399"/>
+        <item x="29"/>
+        <item x="278"/>
+        <item x="131"/>
+        <item x="124"/>
+        <item x="357"/>
+        <item x="245"/>
+        <item x="228"/>
+        <item x="97"/>
+        <item x="100"/>
+        <item x="89"/>
+        <item x="227"/>
+        <item x="5"/>
+        <item x="263"/>
+        <item x="108"/>
+        <item x="358"/>
+        <item x="210"/>
+        <item x="239"/>
+        <item x="281"/>
+        <item x="175"/>
+        <item x="193"/>
+        <item x="179"/>
+        <item x="361"/>
+        <item x="51"/>
+        <item x="1"/>
+        <item x="317"/>
+        <item x="266"/>
+        <item x="65"/>
+        <item x="391"/>
+        <item x="40"/>
+        <item x="244"/>
+        <item x="160"/>
+        <item x="162"/>
+        <item x="291"/>
+        <item x="191"/>
+        <item x="173"/>
+        <item x="133"/>
+        <item x="256"/>
+        <item x="88"/>
+        <item x="370"/>
+        <item x="102"/>
+        <item x="330"/>
+        <item x="365"/>
+        <item x="35"/>
+        <item x="164"/>
+        <item x="284"/>
+        <item x="107"/>
+        <item x="318"/>
+        <item x="24"/>
+        <item x="48"/>
+        <item x="165"/>
+        <item x="176"/>
+        <item x="344"/>
+        <item x="240"/>
+        <item x="379"/>
+        <item x="304"/>
+        <item x="151"/>
+        <item x="313"/>
+        <item x="295"/>
+        <item x="273"/>
+        <item x="233"/>
+        <item x="42"/>
+        <item x="87"/>
+        <item x="308"/>
+        <item x="16"/>
+        <item x="126"/>
+        <item x="70"/>
+        <item x="285"/>
+        <item x="350"/>
+        <item x="73"/>
+        <item x="250"/>
+        <item x="257"/>
+        <item x="343"/>
+        <item x="329"/>
+        <item x="177"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="61"/>
+        <item x="147"/>
+        <item x="169"/>
+        <item x="104"/>
+        <item x="325"/>
+        <item x="241"/>
+        <item x="386"/>
+        <item x="43"/>
+        <item x="214"/>
+        <item x="25"/>
+        <item x="174"/>
+        <item x="338"/>
+        <item x="167"/>
+        <item x="59"/>
+        <item x="222"/>
+        <item x="331"/>
+        <item x="76"/>
+        <item x="11"/>
+        <item x="192"/>
+        <item x="390"/>
+        <item x="389"/>
+        <item x="106"/>
+        <item x="287"/>
+        <item x="197"/>
+        <item x="302"/>
+        <item x="404"/>
+        <item x="54"/>
+        <item x="381"/>
+        <item x="246"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="201"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="265"/>
+        <item x="86"/>
+        <item x="345"/>
+        <item x="63"/>
+        <item x="91"/>
+        <item x="39"/>
+        <item x="93"/>
+        <item x="270"/>
+        <item x="229"/>
+        <item x="161"/>
+        <item x="387"/>
+        <item x="149"/>
+        <item x="231"/>
+        <item x="23"/>
+        <item x="15"/>
+        <item x="209"/>
+        <item x="31"/>
+        <item x="139"/>
+        <item x="56"/>
+        <item x="7"/>
+        <item x="369"/>
+        <item x="109"/>
+        <item x="253"/>
+        <item x="396"/>
+        <item x="375"/>
+        <item x="119"/>
+        <item x="303"/>
+        <item x="71"/>
+        <item x="403"/>
+        <item x="312"/>
+        <item x="247"/>
+        <item x="112"/>
+        <item x="136"/>
+        <item x="64"/>
+        <item x="60"/>
+        <item x="374"/>
+        <item x="340"/>
+        <item x="288"/>
+        <item x="326"/>
+        <item x="130"/>
+        <item x="339"/>
+        <item x="293"/>
+        <item x="45"/>
+        <item x="276"/>
+        <item x="323"/>
+        <item x="271"/>
+        <item x="311"/>
+        <item x="0"/>
+        <item x="310"/>
+        <item x="322"/>
+        <item x="337"/>
+        <item x="72"/>
+        <item x="128"/>
+        <item x="157"/>
+        <item x="363"/>
+        <item x="18"/>
+        <item x="154"/>
+        <item x="249"/>
+        <item x="155"/>
+        <item x="75"/>
+        <item x="138"/>
+        <item x="260"/>
+        <item x="205"/>
+        <item x="299"/>
+        <item x="94"/>
+        <item x="277"/>
+        <item x="321"/>
+        <item x="49"/>
+        <item x="26"/>
+        <item x="274"/>
+        <item x="306"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="42">
+        <item x="29"/>
+        <item x="23"/>
+        <item x="37"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="33"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="39"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="34"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="31"/>
+        <item x="22"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="26"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="35"/>
+        <item x="10"/>
+        <item x="32"/>
+        <item x="36"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="20"/>
+        <item x="24"/>
+        <item x="40"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Purchase_Amount" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="9" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F1EBD4B-C807-4D4D-9319-35309CF490CE}" name="5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gender">
+  <location ref="A15:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="406">
+        <item x="2"/>
+        <item x="132"/>
+        <item x="166"/>
+        <item x="189"/>
+        <item x="307"/>
+        <item x="44"/>
+        <item x="234"/>
+        <item x="360"/>
+        <item x="145"/>
+        <item x="289"/>
+        <item x="258"/>
+        <item x="380"/>
+        <item x="74"/>
+        <item x="334"/>
+        <item x="213"/>
+        <item x="382"/>
+        <item x="255"/>
+        <item x="142"/>
+        <item x="232"/>
+        <item x="92"/>
+        <item x="14"/>
+        <item x="46"/>
+        <item x="353"/>
+        <item x="243"/>
+        <item x="67"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="203"/>
+        <item x="208"/>
+        <item x="314"/>
+        <item x="17"/>
+        <item x="309"/>
+        <item x="272"/>
+        <item x="199"/>
+        <item x="349"/>
+        <item x="183"/>
+        <item x="96"/>
+        <item x="393"/>
+        <item x="346"/>
+        <item x="372"/>
+        <item x="268"/>
+        <item x="212"/>
+        <item x="111"/>
+        <item x="230"/>
+        <item x="221"/>
+        <item x="206"/>
+        <item x="336"/>
+        <item x="202"/>
+        <item x="269"/>
+        <item x="388"/>
+        <item x="238"/>
+        <item x="53"/>
+        <item x="254"/>
+        <item x="316"/>
+        <item x="319"/>
+        <item x="220"/>
+        <item x="200"/>
+        <item x="159"/>
+        <item x="216"/>
+        <item x="117"/>
+        <item x="352"/>
+        <item x="315"/>
+        <item x="292"/>
+        <item x="156"/>
+        <item x="261"/>
+        <item x="190"/>
+        <item x="113"/>
+        <item x="280"/>
+        <item x="146"/>
+        <item x="150"/>
+        <item x="172"/>
+        <item x="12"/>
+        <item x="19"/>
+        <item x="366"/>
+        <item x="262"/>
+        <item x="223"/>
+        <item x="52"/>
+        <item x="347"/>
+        <item x="81"/>
+        <item x="68"/>
+        <item x="402"/>
+        <item x="37"/>
+        <item x="305"/>
+        <item x="36"/>
+        <item x="395"/>
+        <item x="368"/>
+        <item x="77"/>
+        <item x="98"/>
+        <item x="171"/>
+        <item x="135"/>
+        <item x="400"/>
+        <item x="267"/>
+        <item x="217"/>
+        <item x="110"/>
+        <item x="134"/>
+        <item x="196"/>
+        <item x="298"/>
+        <item x="335"/>
+        <item x="185"/>
+        <item x="373"/>
+        <item x="55"/>
+        <item x="103"/>
+        <item x="351"/>
+        <item x="28"/>
+        <item x="50"/>
+        <item x="359"/>
+        <item x="327"/>
+        <item x="153"/>
+        <item x="181"/>
+        <item x="286"/>
+        <item x="401"/>
+        <item x="123"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="182"/>
+        <item x="204"/>
+        <item x="80"/>
+        <item x="4"/>
+        <item x="69"/>
+        <item x="143"/>
+        <item x="279"/>
+        <item x="186"/>
+        <item x="364"/>
+        <item x="301"/>
+        <item x="376"/>
+        <item x="342"/>
+        <item x="195"/>
+        <item x="148"/>
+        <item x="10"/>
+        <item x="320"/>
+        <item x="83"/>
+        <item x="235"/>
+        <item x="79"/>
+        <item x="251"/>
+        <item x="394"/>
+        <item x="332"/>
+        <item x="137"/>
+        <item x="259"/>
+        <item x="118"/>
+        <item x="99"/>
+        <item x="141"/>
+        <item x="188"/>
+        <item x="101"/>
+        <item x="398"/>
+        <item x="392"/>
+        <item x="356"/>
+        <item x="58"/>
+        <item x="180"/>
+        <item x="82"/>
+        <item x="211"/>
+        <item x="282"/>
+        <item x="3"/>
+        <item x="275"/>
+        <item x="225"/>
+        <item x="252"/>
+        <item x="355"/>
+        <item x="297"/>
+        <item x="283"/>
+        <item x="27"/>
+        <item x="354"/>
+        <item x="90"/>
+        <item x="371"/>
+        <item x="384"/>
+        <item x="168"/>
+        <item x="66"/>
+        <item x="341"/>
+        <item x="362"/>
+        <item x="129"/>
+        <item x="30"/>
+        <item x="294"/>
+        <item x="6"/>
+        <item x="115"/>
+        <item x="218"/>
+        <item x="105"/>
+        <item x="163"/>
+        <item x="224"/>
+        <item x="125"/>
+        <item x="328"/>
+        <item x="207"/>
+        <item x="120"/>
+        <item x="397"/>
+        <item x="21"/>
+        <item x="264"/>
+        <item x="333"/>
+        <item x="236"/>
+        <item x="300"/>
+        <item x="198"/>
+        <item x="226"/>
+        <item x="348"/>
+        <item x="383"/>
+        <item x="324"/>
+        <item x="385"/>
+        <item x="290"/>
+        <item x="144"/>
+        <item x="121"/>
+        <item x="62"/>
+        <item x="140"/>
+        <item x="215"/>
+        <item x="367"/>
+        <item x="122"/>
+        <item x="219"/>
+        <item x="178"/>
+        <item x="170"/>
+        <item x="13"/>
+        <item x="47"/>
+        <item x="194"/>
+        <item x="152"/>
+        <item x="95"/>
+        <item x="187"/>
+        <item x="158"/>
+        <item x="248"/>
+        <item x="242"/>
+        <item x="184"/>
+        <item x="296"/>
+        <item x="127"/>
+        <item x="114"/>
+        <item x="116"/>
+        <item x="237"/>
+        <item x="399"/>
+        <item x="29"/>
+        <item x="278"/>
+        <item x="131"/>
+        <item x="124"/>
+        <item x="357"/>
+        <item x="245"/>
+        <item x="228"/>
+        <item x="97"/>
+        <item x="100"/>
+        <item x="89"/>
+        <item x="227"/>
+        <item x="5"/>
+        <item x="263"/>
+        <item x="108"/>
+        <item x="358"/>
+        <item x="210"/>
+        <item x="239"/>
+        <item x="281"/>
+        <item x="175"/>
+        <item x="193"/>
+        <item x="179"/>
+        <item x="361"/>
+        <item x="51"/>
+        <item x="1"/>
+        <item x="317"/>
+        <item x="266"/>
+        <item x="65"/>
+        <item x="391"/>
+        <item x="40"/>
+        <item x="244"/>
+        <item x="160"/>
+        <item x="162"/>
+        <item x="291"/>
+        <item x="191"/>
+        <item x="173"/>
+        <item x="133"/>
+        <item x="256"/>
+        <item x="88"/>
+        <item x="370"/>
+        <item x="102"/>
+        <item x="330"/>
+        <item x="365"/>
+        <item x="35"/>
+        <item x="164"/>
+        <item x="284"/>
+        <item x="107"/>
+        <item x="318"/>
+        <item x="24"/>
+        <item x="48"/>
+        <item x="165"/>
+        <item x="176"/>
+        <item x="344"/>
+        <item x="240"/>
+        <item x="379"/>
+        <item x="304"/>
+        <item x="151"/>
+        <item x="313"/>
+        <item x="295"/>
+        <item x="273"/>
+        <item x="233"/>
+        <item x="42"/>
+        <item x="87"/>
+        <item x="308"/>
+        <item x="16"/>
+        <item x="126"/>
+        <item x="70"/>
+        <item x="285"/>
+        <item x="350"/>
+        <item x="73"/>
+        <item x="250"/>
+        <item x="257"/>
+        <item x="343"/>
+        <item x="329"/>
+        <item x="177"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="61"/>
+        <item x="147"/>
+        <item x="169"/>
+        <item x="104"/>
+        <item x="325"/>
+        <item x="241"/>
+        <item x="386"/>
+        <item x="43"/>
+        <item x="214"/>
+        <item x="25"/>
+        <item x="174"/>
+        <item x="338"/>
+        <item x="167"/>
+        <item x="59"/>
+        <item x="222"/>
+        <item x="331"/>
+        <item x="76"/>
+        <item x="11"/>
+        <item x="192"/>
+        <item x="390"/>
+        <item x="389"/>
+        <item x="106"/>
+        <item x="287"/>
+        <item x="197"/>
+        <item x="302"/>
+        <item x="404"/>
+        <item x="54"/>
+        <item x="381"/>
+        <item x="246"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="201"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="265"/>
+        <item x="86"/>
+        <item x="345"/>
+        <item x="63"/>
+        <item x="91"/>
+        <item x="39"/>
+        <item x="93"/>
+        <item x="270"/>
+        <item x="229"/>
+        <item x="161"/>
+        <item x="387"/>
+        <item x="149"/>
+        <item x="231"/>
+        <item x="23"/>
+        <item x="15"/>
+        <item x="209"/>
+        <item x="31"/>
+        <item x="139"/>
+        <item x="56"/>
+        <item x="7"/>
+        <item x="369"/>
+        <item x="109"/>
+        <item x="253"/>
+        <item x="396"/>
+        <item x="375"/>
+        <item x="119"/>
+        <item x="303"/>
+        <item x="71"/>
+        <item x="403"/>
+        <item x="312"/>
+        <item x="247"/>
+        <item x="112"/>
+        <item x="136"/>
+        <item x="64"/>
+        <item x="60"/>
+        <item x="374"/>
+        <item x="340"/>
+        <item x="288"/>
+        <item x="326"/>
+        <item x="130"/>
+        <item x="339"/>
+        <item x="293"/>
+        <item x="45"/>
+        <item x="276"/>
+        <item x="323"/>
+        <item x="271"/>
+        <item x="311"/>
+        <item x="0"/>
+        <item x="310"/>
+        <item x="322"/>
+        <item x="337"/>
+        <item x="72"/>
+        <item x="128"/>
+        <item x="157"/>
+        <item x="363"/>
+        <item x="18"/>
+        <item x="154"/>
+        <item x="249"/>
+        <item x="155"/>
+        <item x="75"/>
+        <item x="138"/>
+        <item x="260"/>
+        <item x="205"/>
+        <item x="299"/>
+        <item x="94"/>
+        <item x="277"/>
+        <item x="321"/>
+        <item x="49"/>
+        <item x="26"/>
+        <item x="274"/>
+        <item x="306"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de Gender" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{139E99D0-5092-4B36-83C3-676BF3C56F33}" name="3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Product_Category">
   <location ref="G3:H10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -21557,7 +22684,7 @@
     <dataField name="Suma de Purchase_Amount" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -21818,7 +22945,519 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17448897-6334-48FA-B89F-D9C989051F70}" name="2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Country">
+  <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="406">
+        <item x="2"/>
+        <item x="132"/>
+        <item x="166"/>
+        <item x="189"/>
+        <item x="307"/>
+        <item x="44"/>
+        <item x="234"/>
+        <item x="360"/>
+        <item x="145"/>
+        <item x="289"/>
+        <item x="258"/>
+        <item x="380"/>
+        <item x="74"/>
+        <item x="334"/>
+        <item x="213"/>
+        <item x="382"/>
+        <item x="255"/>
+        <item x="142"/>
+        <item x="232"/>
+        <item x="92"/>
+        <item x="14"/>
+        <item x="46"/>
+        <item x="353"/>
+        <item x="243"/>
+        <item x="67"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="203"/>
+        <item x="208"/>
+        <item x="314"/>
+        <item x="17"/>
+        <item x="309"/>
+        <item x="272"/>
+        <item x="199"/>
+        <item x="349"/>
+        <item x="183"/>
+        <item x="96"/>
+        <item x="393"/>
+        <item x="346"/>
+        <item x="372"/>
+        <item x="268"/>
+        <item x="212"/>
+        <item x="111"/>
+        <item x="230"/>
+        <item x="221"/>
+        <item x="206"/>
+        <item x="336"/>
+        <item x="202"/>
+        <item x="269"/>
+        <item x="388"/>
+        <item x="238"/>
+        <item x="53"/>
+        <item x="254"/>
+        <item x="316"/>
+        <item x="319"/>
+        <item x="220"/>
+        <item x="200"/>
+        <item x="159"/>
+        <item x="216"/>
+        <item x="117"/>
+        <item x="352"/>
+        <item x="315"/>
+        <item x="292"/>
+        <item x="156"/>
+        <item x="261"/>
+        <item x="190"/>
+        <item x="113"/>
+        <item x="280"/>
+        <item x="146"/>
+        <item x="150"/>
+        <item x="172"/>
+        <item x="12"/>
+        <item x="19"/>
+        <item x="366"/>
+        <item x="262"/>
+        <item x="223"/>
+        <item x="52"/>
+        <item x="347"/>
+        <item x="81"/>
+        <item x="68"/>
+        <item x="402"/>
+        <item x="37"/>
+        <item x="305"/>
+        <item x="36"/>
+        <item x="395"/>
+        <item x="368"/>
+        <item x="77"/>
+        <item x="98"/>
+        <item x="171"/>
+        <item x="135"/>
+        <item x="400"/>
+        <item x="267"/>
+        <item x="217"/>
+        <item x="110"/>
+        <item x="134"/>
+        <item x="196"/>
+        <item x="298"/>
+        <item x="335"/>
+        <item x="185"/>
+        <item x="373"/>
+        <item x="55"/>
+        <item x="103"/>
+        <item x="351"/>
+        <item x="28"/>
+        <item x="50"/>
+        <item x="359"/>
+        <item x="327"/>
+        <item x="153"/>
+        <item x="181"/>
+        <item x="286"/>
+        <item x="401"/>
+        <item x="123"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="182"/>
+        <item x="204"/>
+        <item x="80"/>
+        <item x="4"/>
+        <item x="69"/>
+        <item x="143"/>
+        <item x="279"/>
+        <item x="186"/>
+        <item x="364"/>
+        <item x="301"/>
+        <item x="376"/>
+        <item x="342"/>
+        <item x="195"/>
+        <item x="148"/>
+        <item x="10"/>
+        <item x="320"/>
+        <item x="83"/>
+        <item x="235"/>
+        <item x="79"/>
+        <item x="251"/>
+        <item x="394"/>
+        <item x="332"/>
+        <item x="137"/>
+        <item x="259"/>
+        <item x="118"/>
+        <item x="99"/>
+        <item x="141"/>
+        <item x="188"/>
+        <item x="101"/>
+        <item x="398"/>
+        <item x="392"/>
+        <item x="356"/>
+        <item x="58"/>
+        <item x="180"/>
+        <item x="82"/>
+        <item x="211"/>
+        <item x="282"/>
+        <item x="3"/>
+        <item x="275"/>
+        <item x="225"/>
+        <item x="252"/>
+        <item x="355"/>
+        <item x="297"/>
+        <item x="283"/>
+        <item x="27"/>
+        <item x="354"/>
+        <item x="90"/>
+        <item x="371"/>
+        <item x="384"/>
+        <item x="168"/>
+        <item x="66"/>
+        <item x="341"/>
+        <item x="362"/>
+        <item x="129"/>
+        <item x="30"/>
+        <item x="294"/>
+        <item x="6"/>
+        <item x="115"/>
+        <item x="218"/>
+        <item x="105"/>
+        <item x="163"/>
+        <item x="224"/>
+        <item x="125"/>
+        <item x="328"/>
+        <item x="207"/>
+        <item x="120"/>
+        <item x="397"/>
+        <item x="21"/>
+        <item x="264"/>
+        <item x="333"/>
+        <item x="236"/>
+        <item x="300"/>
+        <item x="198"/>
+        <item x="226"/>
+        <item x="348"/>
+        <item x="383"/>
+        <item x="324"/>
+        <item x="385"/>
+        <item x="290"/>
+        <item x="144"/>
+        <item x="121"/>
+        <item x="62"/>
+        <item x="140"/>
+        <item x="215"/>
+        <item x="367"/>
+        <item x="122"/>
+        <item x="219"/>
+        <item x="178"/>
+        <item x="170"/>
+        <item x="13"/>
+        <item x="47"/>
+        <item x="194"/>
+        <item x="152"/>
+        <item x="95"/>
+        <item x="187"/>
+        <item x="158"/>
+        <item x="248"/>
+        <item x="242"/>
+        <item x="184"/>
+        <item x="296"/>
+        <item x="127"/>
+        <item x="114"/>
+        <item x="116"/>
+        <item x="237"/>
+        <item x="399"/>
+        <item x="29"/>
+        <item x="278"/>
+        <item x="131"/>
+        <item x="124"/>
+        <item x="357"/>
+        <item x="245"/>
+        <item x="228"/>
+        <item x="97"/>
+        <item x="100"/>
+        <item x="89"/>
+        <item x="227"/>
+        <item x="5"/>
+        <item x="263"/>
+        <item x="108"/>
+        <item x="358"/>
+        <item x="210"/>
+        <item x="239"/>
+        <item x="281"/>
+        <item x="175"/>
+        <item x="193"/>
+        <item x="179"/>
+        <item x="361"/>
+        <item x="51"/>
+        <item x="1"/>
+        <item x="317"/>
+        <item x="266"/>
+        <item x="65"/>
+        <item x="391"/>
+        <item x="40"/>
+        <item x="244"/>
+        <item x="160"/>
+        <item x="162"/>
+        <item x="291"/>
+        <item x="191"/>
+        <item x="173"/>
+        <item x="133"/>
+        <item x="256"/>
+        <item x="88"/>
+        <item x="370"/>
+        <item x="102"/>
+        <item x="330"/>
+        <item x="365"/>
+        <item x="35"/>
+        <item x="164"/>
+        <item x="284"/>
+        <item x="107"/>
+        <item x="318"/>
+        <item x="24"/>
+        <item x="48"/>
+        <item x="165"/>
+        <item x="176"/>
+        <item x="344"/>
+        <item x="240"/>
+        <item x="379"/>
+        <item x="304"/>
+        <item x="151"/>
+        <item x="313"/>
+        <item x="295"/>
+        <item x="273"/>
+        <item x="233"/>
+        <item x="42"/>
+        <item x="87"/>
+        <item x="308"/>
+        <item x="16"/>
+        <item x="126"/>
+        <item x="70"/>
+        <item x="285"/>
+        <item x="350"/>
+        <item x="73"/>
+        <item x="250"/>
+        <item x="257"/>
+        <item x="343"/>
+        <item x="329"/>
+        <item x="177"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="61"/>
+        <item x="147"/>
+        <item x="169"/>
+        <item x="104"/>
+        <item x="325"/>
+        <item x="241"/>
+        <item x="386"/>
+        <item x="43"/>
+        <item x="214"/>
+        <item x="25"/>
+        <item x="174"/>
+        <item x="338"/>
+        <item x="167"/>
+        <item x="59"/>
+        <item x="222"/>
+        <item x="331"/>
+        <item x="76"/>
+        <item x="11"/>
+        <item x="192"/>
+        <item x="390"/>
+        <item x="389"/>
+        <item x="106"/>
+        <item x="287"/>
+        <item x="197"/>
+        <item x="302"/>
+        <item x="404"/>
+        <item x="54"/>
+        <item x="381"/>
+        <item x="246"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="201"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="265"/>
+        <item x="86"/>
+        <item x="345"/>
+        <item x="63"/>
+        <item x="91"/>
+        <item x="39"/>
+        <item x="93"/>
+        <item x="270"/>
+        <item x="229"/>
+        <item x="161"/>
+        <item x="387"/>
+        <item x="149"/>
+        <item x="231"/>
+        <item x="23"/>
+        <item x="15"/>
+        <item x="209"/>
+        <item x="31"/>
+        <item x="139"/>
+        <item x="56"/>
+        <item x="7"/>
+        <item x="369"/>
+        <item x="109"/>
+        <item x="253"/>
+        <item x="396"/>
+        <item x="375"/>
+        <item x="119"/>
+        <item x="303"/>
+        <item x="71"/>
+        <item x="403"/>
+        <item x="312"/>
+        <item x="247"/>
+        <item x="112"/>
+        <item x="136"/>
+        <item x="64"/>
+        <item x="60"/>
+        <item x="374"/>
+        <item x="340"/>
+        <item x="288"/>
+        <item x="326"/>
+        <item x="130"/>
+        <item x="339"/>
+        <item x="293"/>
+        <item x="45"/>
+        <item x="276"/>
+        <item x="323"/>
+        <item x="271"/>
+        <item x="311"/>
+        <item x="0"/>
+        <item x="310"/>
+        <item x="322"/>
+        <item x="337"/>
+        <item x="72"/>
+        <item x="128"/>
+        <item x="157"/>
+        <item x="363"/>
+        <item x="18"/>
+        <item x="154"/>
+        <item x="249"/>
+        <item x="155"/>
+        <item x="75"/>
+        <item x="138"/>
+        <item x="260"/>
+        <item x="205"/>
+        <item x="299"/>
+        <item x="94"/>
+        <item x="277"/>
+        <item x="321"/>
+        <item x="49"/>
+        <item x="26"/>
+        <item x="274"/>
+        <item x="306"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Promedio de Purchase_Amount" fld="6" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8B51822-7413-416F-9EB1-32927AF0D99E}" name="1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Country">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -22758,7 +24397,612 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2A75BE5-3A20-4653-8B73-8C85146E8AE7}" name="7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="G15:H57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField numFmtId="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField numFmtId="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField numFmtId="14" showAll="0" defaultSubtotal="0">
+      <items count="405">
+        <item x="2"/>
+        <item x="132"/>
+        <item x="166"/>
+        <item x="189"/>
+        <item x="307"/>
+        <item x="44"/>
+        <item x="234"/>
+        <item x="360"/>
+        <item x="145"/>
+        <item x="289"/>
+        <item x="258"/>
+        <item x="380"/>
+        <item x="74"/>
+        <item x="334"/>
+        <item x="213"/>
+        <item x="382"/>
+        <item x="255"/>
+        <item x="142"/>
+        <item x="232"/>
+        <item x="92"/>
+        <item x="14"/>
+        <item x="46"/>
+        <item x="353"/>
+        <item x="243"/>
+        <item x="67"/>
+        <item x="85"/>
+        <item x="84"/>
+        <item x="203"/>
+        <item x="208"/>
+        <item x="314"/>
+        <item x="17"/>
+        <item x="309"/>
+        <item x="272"/>
+        <item x="199"/>
+        <item x="349"/>
+        <item x="183"/>
+        <item x="96"/>
+        <item x="393"/>
+        <item x="346"/>
+        <item x="372"/>
+        <item x="268"/>
+        <item x="212"/>
+        <item x="111"/>
+        <item x="230"/>
+        <item x="221"/>
+        <item x="206"/>
+        <item x="336"/>
+        <item x="202"/>
+        <item x="269"/>
+        <item x="388"/>
+        <item x="238"/>
+        <item x="53"/>
+        <item x="254"/>
+        <item x="316"/>
+        <item x="319"/>
+        <item x="220"/>
+        <item x="200"/>
+        <item x="159"/>
+        <item x="216"/>
+        <item x="117"/>
+        <item x="352"/>
+        <item x="315"/>
+        <item x="292"/>
+        <item x="156"/>
+        <item x="261"/>
+        <item x="190"/>
+        <item x="113"/>
+        <item x="280"/>
+        <item x="146"/>
+        <item x="150"/>
+        <item x="172"/>
+        <item x="12"/>
+        <item x="19"/>
+        <item x="366"/>
+        <item x="262"/>
+        <item x="223"/>
+        <item x="52"/>
+        <item x="347"/>
+        <item x="81"/>
+        <item x="68"/>
+        <item x="402"/>
+        <item x="37"/>
+        <item x="305"/>
+        <item x="36"/>
+        <item x="395"/>
+        <item x="368"/>
+        <item x="77"/>
+        <item x="98"/>
+        <item x="171"/>
+        <item x="135"/>
+        <item x="400"/>
+        <item x="267"/>
+        <item x="217"/>
+        <item x="110"/>
+        <item x="134"/>
+        <item x="196"/>
+        <item x="298"/>
+        <item x="335"/>
+        <item x="185"/>
+        <item x="373"/>
+        <item x="55"/>
+        <item x="103"/>
+        <item x="351"/>
+        <item x="28"/>
+        <item x="50"/>
+        <item x="359"/>
+        <item x="327"/>
+        <item x="153"/>
+        <item x="181"/>
+        <item x="286"/>
+        <item x="401"/>
+        <item x="123"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="182"/>
+        <item x="204"/>
+        <item x="80"/>
+        <item x="4"/>
+        <item x="69"/>
+        <item x="143"/>
+        <item x="279"/>
+        <item x="186"/>
+        <item x="364"/>
+        <item x="301"/>
+        <item x="376"/>
+        <item x="342"/>
+        <item x="195"/>
+        <item x="148"/>
+        <item x="10"/>
+        <item x="320"/>
+        <item x="83"/>
+        <item x="235"/>
+        <item x="79"/>
+        <item x="251"/>
+        <item x="394"/>
+        <item x="332"/>
+        <item x="137"/>
+        <item x="259"/>
+        <item x="118"/>
+        <item x="99"/>
+        <item x="141"/>
+        <item x="188"/>
+        <item x="101"/>
+        <item x="398"/>
+        <item x="392"/>
+        <item x="356"/>
+        <item x="58"/>
+        <item x="180"/>
+        <item x="82"/>
+        <item x="211"/>
+        <item x="282"/>
+        <item x="3"/>
+        <item x="275"/>
+        <item x="225"/>
+        <item x="252"/>
+        <item x="355"/>
+        <item x="297"/>
+        <item x="283"/>
+        <item x="27"/>
+        <item x="354"/>
+        <item x="90"/>
+        <item x="371"/>
+        <item x="384"/>
+        <item x="168"/>
+        <item x="66"/>
+        <item x="341"/>
+        <item x="362"/>
+        <item x="129"/>
+        <item x="30"/>
+        <item x="294"/>
+        <item x="6"/>
+        <item x="115"/>
+        <item x="218"/>
+        <item x="105"/>
+        <item x="163"/>
+        <item x="224"/>
+        <item x="125"/>
+        <item x="328"/>
+        <item x="207"/>
+        <item x="120"/>
+        <item x="397"/>
+        <item x="21"/>
+        <item x="264"/>
+        <item x="333"/>
+        <item x="236"/>
+        <item x="300"/>
+        <item x="198"/>
+        <item x="226"/>
+        <item x="348"/>
+        <item x="383"/>
+        <item x="324"/>
+        <item x="385"/>
+        <item x="290"/>
+        <item x="144"/>
+        <item x="121"/>
+        <item x="62"/>
+        <item x="140"/>
+        <item x="215"/>
+        <item x="367"/>
+        <item x="122"/>
+        <item x="219"/>
+        <item x="178"/>
+        <item x="170"/>
+        <item x="13"/>
+        <item x="47"/>
+        <item x="194"/>
+        <item x="152"/>
+        <item x="95"/>
+        <item x="187"/>
+        <item x="158"/>
+        <item x="248"/>
+        <item x="242"/>
+        <item x="184"/>
+        <item x="296"/>
+        <item x="127"/>
+        <item x="114"/>
+        <item x="116"/>
+        <item x="237"/>
+        <item x="399"/>
+        <item x="29"/>
+        <item x="278"/>
+        <item x="131"/>
+        <item x="124"/>
+        <item x="357"/>
+        <item x="245"/>
+        <item x="228"/>
+        <item x="97"/>
+        <item x="100"/>
+        <item x="89"/>
+        <item x="227"/>
+        <item x="5"/>
+        <item x="263"/>
+        <item x="108"/>
+        <item x="358"/>
+        <item x="210"/>
+        <item x="239"/>
+        <item x="281"/>
+        <item x="175"/>
+        <item x="193"/>
+        <item x="179"/>
+        <item x="361"/>
+        <item x="51"/>
+        <item x="1"/>
+        <item x="317"/>
+        <item x="266"/>
+        <item x="65"/>
+        <item x="391"/>
+        <item x="40"/>
+        <item x="244"/>
+        <item x="160"/>
+        <item x="162"/>
+        <item x="291"/>
+        <item x="191"/>
+        <item x="173"/>
+        <item x="133"/>
+        <item x="256"/>
+        <item x="88"/>
+        <item x="370"/>
+        <item x="102"/>
+        <item x="330"/>
+        <item x="365"/>
+        <item x="35"/>
+        <item x="164"/>
+        <item x="284"/>
+        <item x="107"/>
+        <item x="318"/>
+        <item x="24"/>
+        <item x="48"/>
+        <item x="165"/>
+        <item x="176"/>
+        <item x="344"/>
+        <item x="240"/>
+        <item x="379"/>
+        <item x="304"/>
+        <item x="151"/>
+        <item x="313"/>
+        <item x="295"/>
+        <item x="273"/>
+        <item x="233"/>
+        <item x="42"/>
+        <item x="87"/>
+        <item x="308"/>
+        <item x="16"/>
+        <item x="126"/>
+        <item x="70"/>
+        <item x="285"/>
+        <item x="350"/>
+        <item x="73"/>
+        <item x="250"/>
+        <item x="257"/>
+        <item x="343"/>
+        <item x="329"/>
+        <item x="177"/>
+        <item x="33"/>
+        <item x="78"/>
+        <item x="34"/>
+        <item x="38"/>
+        <item x="61"/>
+        <item x="147"/>
+        <item x="169"/>
+        <item x="104"/>
+        <item x="325"/>
+        <item x="241"/>
+        <item x="386"/>
+        <item x="43"/>
+        <item x="214"/>
+        <item x="25"/>
+        <item x="174"/>
+        <item x="338"/>
+        <item x="167"/>
+        <item x="59"/>
+        <item x="222"/>
+        <item x="331"/>
+        <item x="76"/>
+        <item x="11"/>
+        <item x="192"/>
+        <item x="390"/>
+        <item x="389"/>
+        <item x="106"/>
+        <item x="287"/>
+        <item x="197"/>
+        <item x="302"/>
+        <item x="404"/>
+        <item x="54"/>
+        <item x="381"/>
+        <item x="246"/>
+        <item x="41"/>
+        <item x="20"/>
+        <item x="32"/>
+        <item x="201"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="57"/>
+        <item x="9"/>
+        <item x="265"/>
+        <item x="86"/>
+        <item x="345"/>
+        <item x="63"/>
+        <item x="91"/>
+        <item x="39"/>
+        <item x="93"/>
+        <item x="270"/>
+        <item x="229"/>
+        <item x="161"/>
+        <item x="387"/>
+        <item x="149"/>
+        <item x="231"/>
+        <item x="23"/>
+        <item x="15"/>
+        <item x="209"/>
+        <item x="31"/>
+        <item x="139"/>
+        <item x="56"/>
+        <item x="7"/>
+        <item x="369"/>
+        <item x="109"/>
+        <item x="253"/>
+        <item x="396"/>
+        <item x="375"/>
+        <item x="119"/>
+        <item x="303"/>
+        <item x="71"/>
+        <item x="403"/>
+        <item x="312"/>
+        <item x="247"/>
+        <item x="112"/>
+        <item x="136"/>
+        <item x="64"/>
+        <item x="60"/>
+        <item x="374"/>
+        <item x="340"/>
+        <item x="288"/>
+        <item x="326"/>
+        <item x="130"/>
+        <item x="339"/>
+        <item x="293"/>
+        <item x="45"/>
+        <item x="276"/>
+        <item x="323"/>
+        <item x="271"/>
+        <item x="311"/>
+        <item x="0"/>
+        <item x="310"/>
+        <item x="322"/>
+        <item x="337"/>
+        <item x="72"/>
+        <item x="128"/>
+        <item x="157"/>
+        <item x="363"/>
+        <item x="18"/>
+        <item x="154"/>
+        <item x="249"/>
+        <item x="155"/>
+        <item x="75"/>
+        <item x="138"/>
+        <item x="260"/>
+        <item x="205"/>
+        <item x="299"/>
+        <item x="94"/>
+        <item x="277"/>
+        <item x="321"/>
+        <item x="49"/>
+        <item x="26"/>
+        <item x="274"/>
+        <item x="306"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="10"/>
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="42">
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Purchase_Amount" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F1AE490-313E-4342-9B71-48204AA13A64}" name="4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Product_Category">
   <location ref="J3:K10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -23355,7 +25599,7 @@
     <dataField name="Promedio de Rating" fld="8" subtotal="average" baseField="7" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -23377,2247 +25621,6 @@
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEB42CE3-9D07-47B6-A5DF-68C03766D442}" name="6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Country">
-  <location ref="D15:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0">
-      <items count="43">
-        <item x="13"/>
-        <item x="19"/>
-        <item x="28"/>
-        <item x="39"/>
-        <item x="11"/>
-        <item x="34"/>
-        <item x="2"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="40"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="38"/>
-        <item x="21"/>
-        <item x="27"/>
-        <item x="15"/>
-        <item x="25"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="41"/>
-        <item x="31"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="3"/>
-        <item x="22"/>
-        <item x="12"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="18"/>
-        <item x="1"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="30"/>
-        <item x="9"/>
-        <item x="23"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="29"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="406">
-        <item x="2"/>
-        <item x="132"/>
-        <item x="166"/>
-        <item x="189"/>
-        <item x="307"/>
-        <item x="44"/>
-        <item x="234"/>
-        <item x="360"/>
-        <item x="145"/>
-        <item x="289"/>
-        <item x="258"/>
-        <item x="380"/>
-        <item x="74"/>
-        <item x="334"/>
-        <item x="213"/>
-        <item x="382"/>
-        <item x="255"/>
-        <item x="142"/>
-        <item x="232"/>
-        <item x="92"/>
-        <item x="14"/>
-        <item x="46"/>
-        <item x="353"/>
-        <item x="243"/>
-        <item x="67"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="203"/>
-        <item x="208"/>
-        <item x="314"/>
-        <item x="17"/>
-        <item x="309"/>
-        <item x="272"/>
-        <item x="199"/>
-        <item x="349"/>
-        <item x="183"/>
-        <item x="96"/>
-        <item x="393"/>
-        <item x="346"/>
-        <item x="372"/>
-        <item x="268"/>
-        <item x="212"/>
-        <item x="111"/>
-        <item x="230"/>
-        <item x="221"/>
-        <item x="206"/>
-        <item x="336"/>
-        <item x="202"/>
-        <item x="269"/>
-        <item x="388"/>
-        <item x="238"/>
-        <item x="53"/>
-        <item x="254"/>
-        <item x="316"/>
-        <item x="319"/>
-        <item x="220"/>
-        <item x="200"/>
-        <item x="159"/>
-        <item x="216"/>
-        <item x="117"/>
-        <item x="352"/>
-        <item x="315"/>
-        <item x="292"/>
-        <item x="156"/>
-        <item x="261"/>
-        <item x="190"/>
-        <item x="113"/>
-        <item x="280"/>
-        <item x="146"/>
-        <item x="150"/>
-        <item x="172"/>
-        <item x="12"/>
-        <item x="19"/>
-        <item x="366"/>
-        <item x="262"/>
-        <item x="223"/>
-        <item x="52"/>
-        <item x="347"/>
-        <item x="81"/>
-        <item x="68"/>
-        <item x="402"/>
-        <item x="37"/>
-        <item x="305"/>
-        <item x="36"/>
-        <item x="395"/>
-        <item x="368"/>
-        <item x="77"/>
-        <item x="98"/>
-        <item x="171"/>
-        <item x="135"/>
-        <item x="400"/>
-        <item x="267"/>
-        <item x="217"/>
-        <item x="110"/>
-        <item x="134"/>
-        <item x="196"/>
-        <item x="298"/>
-        <item x="335"/>
-        <item x="185"/>
-        <item x="373"/>
-        <item x="55"/>
-        <item x="103"/>
-        <item x="351"/>
-        <item x="28"/>
-        <item x="50"/>
-        <item x="359"/>
-        <item x="327"/>
-        <item x="153"/>
-        <item x="181"/>
-        <item x="286"/>
-        <item x="401"/>
-        <item x="123"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="182"/>
-        <item x="204"/>
-        <item x="80"/>
-        <item x="4"/>
-        <item x="69"/>
-        <item x="143"/>
-        <item x="279"/>
-        <item x="186"/>
-        <item x="364"/>
-        <item x="301"/>
-        <item x="376"/>
-        <item x="342"/>
-        <item x="195"/>
-        <item x="148"/>
-        <item x="10"/>
-        <item x="320"/>
-        <item x="83"/>
-        <item x="235"/>
-        <item x="79"/>
-        <item x="251"/>
-        <item x="394"/>
-        <item x="332"/>
-        <item x="137"/>
-        <item x="259"/>
-        <item x="118"/>
-        <item x="99"/>
-        <item x="141"/>
-        <item x="188"/>
-        <item x="101"/>
-        <item x="398"/>
-        <item x="392"/>
-        <item x="356"/>
-        <item x="58"/>
-        <item x="180"/>
-        <item x="82"/>
-        <item x="211"/>
-        <item x="282"/>
-        <item x="3"/>
-        <item x="275"/>
-        <item x="225"/>
-        <item x="252"/>
-        <item x="355"/>
-        <item x="297"/>
-        <item x="283"/>
-        <item x="27"/>
-        <item x="354"/>
-        <item x="90"/>
-        <item x="371"/>
-        <item x="384"/>
-        <item x="168"/>
-        <item x="66"/>
-        <item x="341"/>
-        <item x="362"/>
-        <item x="129"/>
-        <item x="30"/>
-        <item x="294"/>
-        <item x="6"/>
-        <item x="115"/>
-        <item x="218"/>
-        <item x="105"/>
-        <item x="163"/>
-        <item x="224"/>
-        <item x="125"/>
-        <item x="328"/>
-        <item x="207"/>
-        <item x="120"/>
-        <item x="397"/>
-        <item x="21"/>
-        <item x="264"/>
-        <item x="333"/>
-        <item x="236"/>
-        <item x="300"/>
-        <item x="198"/>
-        <item x="226"/>
-        <item x="348"/>
-        <item x="383"/>
-        <item x="324"/>
-        <item x="385"/>
-        <item x="290"/>
-        <item x="144"/>
-        <item x="121"/>
-        <item x="62"/>
-        <item x="140"/>
-        <item x="215"/>
-        <item x="367"/>
-        <item x="122"/>
-        <item x="219"/>
-        <item x="178"/>
-        <item x="170"/>
-        <item x="13"/>
-        <item x="47"/>
-        <item x="194"/>
-        <item x="152"/>
-        <item x="95"/>
-        <item x="187"/>
-        <item x="158"/>
-        <item x="248"/>
-        <item x="242"/>
-        <item x="184"/>
-        <item x="296"/>
-        <item x="127"/>
-        <item x="114"/>
-        <item x="116"/>
-        <item x="237"/>
-        <item x="399"/>
-        <item x="29"/>
-        <item x="278"/>
-        <item x="131"/>
-        <item x="124"/>
-        <item x="357"/>
-        <item x="245"/>
-        <item x="228"/>
-        <item x="97"/>
-        <item x="100"/>
-        <item x="89"/>
-        <item x="227"/>
-        <item x="5"/>
-        <item x="263"/>
-        <item x="108"/>
-        <item x="358"/>
-        <item x="210"/>
-        <item x="239"/>
-        <item x="281"/>
-        <item x="175"/>
-        <item x="193"/>
-        <item x="179"/>
-        <item x="361"/>
-        <item x="51"/>
-        <item x="1"/>
-        <item x="317"/>
-        <item x="266"/>
-        <item x="65"/>
-        <item x="391"/>
-        <item x="40"/>
-        <item x="244"/>
-        <item x="160"/>
-        <item x="162"/>
-        <item x="291"/>
-        <item x="191"/>
-        <item x="173"/>
-        <item x="133"/>
-        <item x="256"/>
-        <item x="88"/>
-        <item x="370"/>
-        <item x="102"/>
-        <item x="330"/>
-        <item x="365"/>
-        <item x="35"/>
-        <item x="164"/>
-        <item x="284"/>
-        <item x="107"/>
-        <item x="318"/>
-        <item x="24"/>
-        <item x="48"/>
-        <item x="165"/>
-        <item x="176"/>
-        <item x="344"/>
-        <item x="240"/>
-        <item x="379"/>
-        <item x="304"/>
-        <item x="151"/>
-        <item x="313"/>
-        <item x="295"/>
-        <item x="273"/>
-        <item x="233"/>
-        <item x="42"/>
-        <item x="87"/>
-        <item x="308"/>
-        <item x="16"/>
-        <item x="126"/>
-        <item x="70"/>
-        <item x="285"/>
-        <item x="350"/>
-        <item x="73"/>
-        <item x="250"/>
-        <item x="257"/>
-        <item x="343"/>
-        <item x="329"/>
-        <item x="177"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="34"/>
-        <item x="38"/>
-        <item x="61"/>
-        <item x="147"/>
-        <item x="169"/>
-        <item x="104"/>
-        <item x="325"/>
-        <item x="241"/>
-        <item x="386"/>
-        <item x="43"/>
-        <item x="214"/>
-        <item x="25"/>
-        <item x="174"/>
-        <item x="338"/>
-        <item x="167"/>
-        <item x="59"/>
-        <item x="222"/>
-        <item x="331"/>
-        <item x="76"/>
-        <item x="11"/>
-        <item x="192"/>
-        <item x="390"/>
-        <item x="389"/>
-        <item x="106"/>
-        <item x="287"/>
-        <item x="197"/>
-        <item x="302"/>
-        <item x="404"/>
-        <item x="54"/>
-        <item x="381"/>
-        <item x="246"/>
-        <item x="41"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="201"/>
-        <item x="22"/>
-        <item x="8"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="265"/>
-        <item x="86"/>
-        <item x="345"/>
-        <item x="63"/>
-        <item x="91"/>
-        <item x="39"/>
-        <item x="93"/>
-        <item x="270"/>
-        <item x="229"/>
-        <item x="161"/>
-        <item x="387"/>
-        <item x="149"/>
-        <item x="231"/>
-        <item x="23"/>
-        <item x="15"/>
-        <item x="209"/>
-        <item x="31"/>
-        <item x="139"/>
-        <item x="56"/>
-        <item x="7"/>
-        <item x="369"/>
-        <item x="109"/>
-        <item x="253"/>
-        <item x="396"/>
-        <item x="375"/>
-        <item x="119"/>
-        <item x="303"/>
-        <item x="71"/>
-        <item x="403"/>
-        <item x="312"/>
-        <item x="247"/>
-        <item x="112"/>
-        <item x="136"/>
-        <item x="64"/>
-        <item x="60"/>
-        <item x="374"/>
-        <item x="340"/>
-        <item x="288"/>
-        <item x="326"/>
-        <item x="130"/>
-        <item x="339"/>
-        <item x="293"/>
-        <item x="45"/>
-        <item x="276"/>
-        <item x="323"/>
-        <item x="271"/>
-        <item x="311"/>
-        <item x="0"/>
-        <item x="310"/>
-        <item x="322"/>
-        <item x="337"/>
-        <item x="72"/>
-        <item x="128"/>
-        <item x="157"/>
-        <item x="363"/>
-        <item x="18"/>
-        <item x="154"/>
-        <item x="249"/>
-        <item x="155"/>
-        <item x="75"/>
-        <item x="138"/>
-        <item x="260"/>
-        <item x="205"/>
-        <item x="299"/>
-        <item x="94"/>
-        <item x="277"/>
-        <item x="321"/>
-        <item x="49"/>
-        <item x="26"/>
-        <item x="274"/>
-        <item x="306"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="42">
-        <item x="29"/>
-        <item x="23"/>
-        <item x="37"/>
-        <item x="13"/>
-        <item x="2"/>
-        <item x="33"/>
-        <item x="14"/>
-        <item x="6"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="39"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="38"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="34"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="31"/>
-        <item x="22"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="26"/>
-        <item x="7"/>
-        <item x="27"/>
-        <item x="35"/>
-        <item x="10"/>
-        <item x="32"/>
-        <item x="36"/>
-        <item x="28"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="20"/>
-        <item x="24"/>
-        <item x="40"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Purchase_Amount" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="2">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="9" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="18" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17448897-6334-48FA-B89F-D9C989051F70}" name="2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Country">
-  <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="406">
-        <item x="2"/>
-        <item x="132"/>
-        <item x="166"/>
-        <item x="189"/>
-        <item x="307"/>
-        <item x="44"/>
-        <item x="234"/>
-        <item x="360"/>
-        <item x="145"/>
-        <item x="289"/>
-        <item x="258"/>
-        <item x="380"/>
-        <item x="74"/>
-        <item x="334"/>
-        <item x="213"/>
-        <item x="382"/>
-        <item x="255"/>
-        <item x="142"/>
-        <item x="232"/>
-        <item x="92"/>
-        <item x="14"/>
-        <item x="46"/>
-        <item x="353"/>
-        <item x="243"/>
-        <item x="67"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="203"/>
-        <item x="208"/>
-        <item x="314"/>
-        <item x="17"/>
-        <item x="309"/>
-        <item x="272"/>
-        <item x="199"/>
-        <item x="349"/>
-        <item x="183"/>
-        <item x="96"/>
-        <item x="393"/>
-        <item x="346"/>
-        <item x="372"/>
-        <item x="268"/>
-        <item x="212"/>
-        <item x="111"/>
-        <item x="230"/>
-        <item x="221"/>
-        <item x="206"/>
-        <item x="336"/>
-        <item x="202"/>
-        <item x="269"/>
-        <item x="388"/>
-        <item x="238"/>
-        <item x="53"/>
-        <item x="254"/>
-        <item x="316"/>
-        <item x="319"/>
-        <item x="220"/>
-        <item x="200"/>
-        <item x="159"/>
-        <item x="216"/>
-        <item x="117"/>
-        <item x="352"/>
-        <item x="315"/>
-        <item x="292"/>
-        <item x="156"/>
-        <item x="261"/>
-        <item x="190"/>
-        <item x="113"/>
-        <item x="280"/>
-        <item x="146"/>
-        <item x="150"/>
-        <item x="172"/>
-        <item x="12"/>
-        <item x="19"/>
-        <item x="366"/>
-        <item x="262"/>
-        <item x="223"/>
-        <item x="52"/>
-        <item x="347"/>
-        <item x="81"/>
-        <item x="68"/>
-        <item x="402"/>
-        <item x="37"/>
-        <item x="305"/>
-        <item x="36"/>
-        <item x="395"/>
-        <item x="368"/>
-        <item x="77"/>
-        <item x="98"/>
-        <item x="171"/>
-        <item x="135"/>
-        <item x="400"/>
-        <item x="267"/>
-        <item x="217"/>
-        <item x="110"/>
-        <item x="134"/>
-        <item x="196"/>
-        <item x="298"/>
-        <item x="335"/>
-        <item x="185"/>
-        <item x="373"/>
-        <item x="55"/>
-        <item x="103"/>
-        <item x="351"/>
-        <item x="28"/>
-        <item x="50"/>
-        <item x="359"/>
-        <item x="327"/>
-        <item x="153"/>
-        <item x="181"/>
-        <item x="286"/>
-        <item x="401"/>
-        <item x="123"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="182"/>
-        <item x="204"/>
-        <item x="80"/>
-        <item x="4"/>
-        <item x="69"/>
-        <item x="143"/>
-        <item x="279"/>
-        <item x="186"/>
-        <item x="364"/>
-        <item x="301"/>
-        <item x="376"/>
-        <item x="342"/>
-        <item x="195"/>
-        <item x="148"/>
-        <item x="10"/>
-        <item x="320"/>
-        <item x="83"/>
-        <item x="235"/>
-        <item x="79"/>
-        <item x="251"/>
-        <item x="394"/>
-        <item x="332"/>
-        <item x="137"/>
-        <item x="259"/>
-        <item x="118"/>
-        <item x="99"/>
-        <item x="141"/>
-        <item x="188"/>
-        <item x="101"/>
-        <item x="398"/>
-        <item x="392"/>
-        <item x="356"/>
-        <item x="58"/>
-        <item x="180"/>
-        <item x="82"/>
-        <item x="211"/>
-        <item x="282"/>
-        <item x="3"/>
-        <item x="275"/>
-        <item x="225"/>
-        <item x="252"/>
-        <item x="355"/>
-        <item x="297"/>
-        <item x="283"/>
-        <item x="27"/>
-        <item x="354"/>
-        <item x="90"/>
-        <item x="371"/>
-        <item x="384"/>
-        <item x="168"/>
-        <item x="66"/>
-        <item x="341"/>
-        <item x="362"/>
-        <item x="129"/>
-        <item x="30"/>
-        <item x="294"/>
-        <item x="6"/>
-        <item x="115"/>
-        <item x="218"/>
-        <item x="105"/>
-        <item x="163"/>
-        <item x="224"/>
-        <item x="125"/>
-        <item x="328"/>
-        <item x="207"/>
-        <item x="120"/>
-        <item x="397"/>
-        <item x="21"/>
-        <item x="264"/>
-        <item x="333"/>
-        <item x="236"/>
-        <item x="300"/>
-        <item x="198"/>
-        <item x="226"/>
-        <item x="348"/>
-        <item x="383"/>
-        <item x="324"/>
-        <item x="385"/>
-        <item x="290"/>
-        <item x="144"/>
-        <item x="121"/>
-        <item x="62"/>
-        <item x="140"/>
-        <item x="215"/>
-        <item x="367"/>
-        <item x="122"/>
-        <item x="219"/>
-        <item x="178"/>
-        <item x="170"/>
-        <item x="13"/>
-        <item x="47"/>
-        <item x="194"/>
-        <item x="152"/>
-        <item x="95"/>
-        <item x="187"/>
-        <item x="158"/>
-        <item x="248"/>
-        <item x="242"/>
-        <item x="184"/>
-        <item x="296"/>
-        <item x="127"/>
-        <item x="114"/>
-        <item x="116"/>
-        <item x="237"/>
-        <item x="399"/>
-        <item x="29"/>
-        <item x="278"/>
-        <item x="131"/>
-        <item x="124"/>
-        <item x="357"/>
-        <item x="245"/>
-        <item x="228"/>
-        <item x="97"/>
-        <item x="100"/>
-        <item x="89"/>
-        <item x="227"/>
-        <item x="5"/>
-        <item x="263"/>
-        <item x="108"/>
-        <item x="358"/>
-        <item x="210"/>
-        <item x="239"/>
-        <item x="281"/>
-        <item x="175"/>
-        <item x="193"/>
-        <item x="179"/>
-        <item x="361"/>
-        <item x="51"/>
-        <item x="1"/>
-        <item x="317"/>
-        <item x="266"/>
-        <item x="65"/>
-        <item x="391"/>
-        <item x="40"/>
-        <item x="244"/>
-        <item x="160"/>
-        <item x="162"/>
-        <item x="291"/>
-        <item x="191"/>
-        <item x="173"/>
-        <item x="133"/>
-        <item x="256"/>
-        <item x="88"/>
-        <item x="370"/>
-        <item x="102"/>
-        <item x="330"/>
-        <item x="365"/>
-        <item x="35"/>
-        <item x="164"/>
-        <item x="284"/>
-        <item x="107"/>
-        <item x="318"/>
-        <item x="24"/>
-        <item x="48"/>
-        <item x="165"/>
-        <item x="176"/>
-        <item x="344"/>
-        <item x="240"/>
-        <item x="379"/>
-        <item x="304"/>
-        <item x="151"/>
-        <item x="313"/>
-        <item x="295"/>
-        <item x="273"/>
-        <item x="233"/>
-        <item x="42"/>
-        <item x="87"/>
-        <item x="308"/>
-        <item x="16"/>
-        <item x="126"/>
-        <item x="70"/>
-        <item x="285"/>
-        <item x="350"/>
-        <item x="73"/>
-        <item x="250"/>
-        <item x="257"/>
-        <item x="343"/>
-        <item x="329"/>
-        <item x="177"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="34"/>
-        <item x="38"/>
-        <item x="61"/>
-        <item x="147"/>
-        <item x="169"/>
-        <item x="104"/>
-        <item x="325"/>
-        <item x="241"/>
-        <item x="386"/>
-        <item x="43"/>
-        <item x="214"/>
-        <item x="25"/>
-        <item x="174"/>
-        <item x="338"/>
-        <item x="167"/>
-        <item x="59"/>
-        <item x="222"/>
-        <item x="331"/>
-        <item x="76"/>
-        <item x="11"/>
-        <item x="192"/>
-        <item x="390"/>
-        <item x="389"/>
-        <item x="106"/>
-        <item x="287"/>
-        <item x="197"/>
-        <item x="302"/>
-        <item x="404"/>
-        <item x="54"/>
-        <item x="381"/>
-        <item x="246"/>
-        <item x="41"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="201"/>
-        <item x="22"/>
-        <item x="8"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="265"/>
-        <item x="86"/>
-        <item x="345"/>
-        <item x="63"/>
-        <item x="91"/>
-        <item x="39"/>
-        <item x="93"/>
-        <item x="270"/>
-        <item x="229"/>
-        <item x="161"/>
-        <item x="387"/>
-        <item x="149"/>
-        <item x="231"/>
-        <item x="23"/>
-        <item x="15"/>
-        <item x="209"/>
-        <item x="31"/>
-        <item x="139"/>
-        <item x="56"/>
-        <item x="7"/>
-        <item x="369"/>
-        <item x="109"/>
-        <item x="253"/>
-        <item x="396"/>
-        <item x="375"/>
-        <item x="119"/>
-        <item x="303"/>
-        <item x="71"/>
-        <item x="403"/>
-        <item x="312"/>
-        <item x="247"/>
-        <item x="112"/>
-        <item x="136"/>
-        <item x="64"/>
-        <item x="60"/>
-        <item x="374"/>
-        <item x="340"/>
-        <item x="288"/>
-        <item x="326"/>
-        <item x="130"/>
-        <item x="339"/>
-        <item x="293"/>
-        <item x="45"/>
-        <item x="276"/>
-        <item x="323"/>
-        <item x="271"/>
-        <item x="311"/>
-        <item x="0"/>
-        <item x="310"/>
-        <item x="322"/>
-        <item x="337"/>
-        <item x="72"/>
-        <item x="128"/>
-        <item x="157"/>
-        <item x="363"/>
-        <item x="18"/>
-        <item x="154"/>
-        <item x="249"/>
-        <item x="155"/>
-        <item x="75"/>
-        <item x="138"/>
-        <item x="260"/>
-        <item x="205"/>
-        <item x="299"/>
-        <item x="94"/>
-        <item x="277"/>
-        <item x="321"/>
-        <item x="49"/>
-        <item x="26"/>
-        <item x="274"/>
-        <item x="306"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Promedio de Purchase_Amount" fld="6" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F1EBD4B-C807-4D4D-9319-35309CF490CE}" name="5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Gender">
-  <location ref="A15:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="406">
-        <item x="2"/>
-        <item x="132"/>
-        <item x="166"/>
-        <item x="189"/>
-        <item x="307"/>
-        <item x="44"/>
-        <item x="234"/>
-        <item x="360"/>
-        <item x="145"/>
-        <item x="289"/>
-        <item x="258"/>
-        <item x="380"/>
-        <item x="74"/>
-        <item x="334"/>
-        <item x="213"/>
-        <item x="382"/>
-        <item x="255"/>
-        <item x="142"/>
-        <item x="232"/>
-        <item x="92"/>
-        <item x="14"/>
-        <item x="46"/>
-        <item x="353"/>
-        <item x="243"/>
-        <item x="67"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="203"/>
-        <item x="208"/>
-        <item x="314"/>
-        <item x="17"/>
-        <item x="309"/>
-        <item x="272"/>
-        <item x="199"/>
-        <item x="349"/>
-        <item x="183"/>
-        <item x="96"/>
-        <item x="393"/>
-        <item x="346"/>
-        <item x="372"/>
-        <item x="268"/>
-        <item x="212"/>
-        <item x="111"/>
-        <item x="230"/>
-        <item x="221"/>
-        <item x="206"/>
-        <item x="336"/>
-        <item x="202"/>
-        <item x="269"/>
-        <item x="388"/>
-        <item x="238"/>
-        <item x="53"/>
-        <item x="254"/>
-        <item x="316"/>
-        <item x="319"/>
-        <item x="220"/>
-        <item x="200"/>
-        <item x="159"/>
-        <item x="216"/>
-        <item x="117"/>
-        <item x="352"/>
-        <item x="315"/>
-        <item x="292"/>
-        <item x="156"/>
-        <item x="261"/>
-        <item x="190"/>
-        <item x="113"/>
-        <item x="280"/>
-        <item x="146"/>
-        <item x="150"/>
-        <item x="172"/>
-        <item x="12"/>
-        <item x="19"/>
-        <item x="366"/>
-        <item x="262"/>
-        <item x="223"/>
-        <item x="52"/>
-        <item x="347"/>
-        <item x="81"/>
-        <item x="68"/>
-        <item x="402"/>
-        <item x="37"/>
-        <item x="305"/>
-        <item x="36"/>
-        <item x="395"/>
-        <item x="368"/>
-        <item x="77"/>
-        <item x="98"/>
-        <item x="171"/>
-        <item x="135"/>
-        <item x="400"/>
-        <item x="267"/>
-        <item x="217"/>
-        <item x="110"/>
-        <item x="134"/>
-        <item x="196"/>
-        <item x="298"/>
-        <item x="335"/>
-        <item x="185"/>
-        <item x="373"/>
-        <item x="55"/>
-        <item x="103"/>
-        <item x="351"/>
-        <item x="28"/>
-        <item x="50"/>
-        <item x="359"/>
-        <item x="327"/>
-        <item x="153"/>
-        <item x="181"/>
-        <item x="286"/>
-        <item x="401"/>
-        <item x="123"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="182"/>
-        <item x="204"/>
-        <item x="80"/>
-        <item x="4"/>
-        <item x="69"/>
-        <item x="143"/>
-        <item x="279"/>
-        <item x="186"/>
-        <item x="364"/>
-        <item x="301"/>
-        <item x="376"/>
-        <item x="342"/>
-        <item x="195"/>
-        <item x="148"/>
-        <item x="10"/>
-        <item x="320"/>
-        <item x="83"/>
-        <item x="235"/>
-        <item x="79"/>
-        <item x="251"/>
-        <item x="394"/>
-        <item x="332"/>
-        <item x="137"/>
-        <item x="259"/>
-        <item x="118"/>
-        <item x="99"/>
-        <item x="141"/>
-        <item x="188"/>
-        <item x="101"/>
-        <item x="398"/>
-        <item x="392"/>
-        <item x="356"/>
-        <item x="58"/>
-        <item x="180"/>
-        <item x="82"/>
-        <item x="211"/>
-        <item x="282"/>
-        <item x="3"/>
-        <item x="275"/>
-        <item x="225"/>
-        <item x="252"/>
-        <item x="355"/>
-        <item x="297"/>
-        <item x="283"/>
-        <item x="27"/>
-        <item x="354"/>
-        <item x="90"/>
-        <item x="371"/>
-        <item x="384"/>
-        <item x="168"/>
-        <item x="66"/>
-        <item x="341"/>
-        <item x="362"/>
-        <item x="129"/>
-        <item x="30"/>
-        <item x="294"/>
-        <item x="6"/>
-        <item x="115"/>
-        <item x="218"/>
-        <item x="105"/>
-        <item x="163"/>
-        <item x="224"/>
-        <item x="125"/>
-        <item x="328"/>
-        <item x="207"/>
-        <item x="120"/>
-        <item x="397"/>
-        <item x="21"/>
-        <item x="264"/>
-        <item x="333"/>
-        <item x="236"/>
-        <item x="300"/>
-        <item x="198"/>
-        <item x="226"/>
-        <item x="348"/>
-        <item x="383"/>
-        <item x="324"/>
-        <item x="385"/>
-        <item x="290"/>
-        <item x="144"/>
-        <item x="121"/>
-        <item x="62"/>
-        <item x="140"/>
-        <item x="215"/>
-        <item x="367"/>
-        <item x="122"/>
-        <item x="219"/>
-        <item x="178"/>
-        <item x="170"/>
-        <item x="13"/>
-        <item x="47"/>
-        <item x="194"/>
-        <item x="152"/>
-        <item x="95"/>
-        <item x="187"/>
-        <item x="158"/>
-        <item x="248"/>
-        <item x="242"/>
-        <item x="184"/>
-        <item x="296"/>
-        <item x="127"/>
-        <item x="114"/>
-        <item x="116"/>
-        <item x="237"/>
-        <item x="399"/>
-        <item x="29"/>
-        <item x="278"/>
-        <item x="131"/>
-        <item x="124"/>
-        <item x="357"/>
-        <item x="245"/>
-        <item x="228"/>
-        <item x="97"/>
-        <item x="100"/>
-        <item x="89"/>
-        <item x="227"/>
-        <item x="5"/>
-        <item x="263"/>
-        <item x="108"/>
-        <item x="358"/>
-        <item x="210"/>
-        <item x="239"/>
-        <item x="281"/>
-        <item x="175"/>
-        <item x="193"/>
-        <item x="179"/>
-        <item x="361"/>
-        <item x="51"/>
-        <item x="1"/>
-        <item x="317"/>
-        <item x="266"/>
-        <item x="65"/>
-        <item x="391"/>
-        <item x="40"/>
-        <item x="244"/>
-        <item x="160"/>
-        <item x="162"/>
-        <item x="291"/>
-        <item x="191"/>
-        <item x="173"/>
-        <item x="133"/>
-        <item x="256"/>
-        <item x="88"/>
-        <item x="370"/>
-        <item x="102"/>
-        <item x="330"/>
-        <item x="365"/>
-        <item x="35"/>
-        <item x="164"/>
-        <item x="284"/>
-        <item x="107"/>
-        <item x="318"/>
-        <item x="24"/>
-        <item x="48"/>
-        <item x="165"/>
-        <item x="176"/>
-        <item x="344"/>
-        <item x="240"/>
-        <item x="379"/>
-        <item x="304"/>
-        <item x="151"/>
-        <item x="313"/>
-        <item x="295"/>
-        <item x="273"/>
-        <item x="233"/>
-        <item x="42"/>
-        <item x="87"/>
-        <item x="308"/>
-        <item x="16"/>
-        <item x="126"/>
-        <item x="70"/>
-        <item x="285"/>
-        <item x="350"/>
-        <item x="73"/>
-        <item x="250"/>
-        <item x="257"/>
-        <item x="343"/>
-        <item x="329"/>
-        <item x="177"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="34"/>
-        <item x="38"/>
-        <item x="61"/>
-        <item x="147"/>
-        <item x="169"/>
-        <item x="104"/>
-        <item x="325"/>
-        <item x="241"/>
-        <item x="386"/>
-        <item x="43"/>
-        <item x="214"/>
-        <item x="25"/>
-        <item x="174"/>
-        <item x="338"/>
-        <item x="167"/>
-        <item x="59"/>
-        <item x="222"/>
-        <item x="331"/>
-        <item x="76"/>
-        <item x="11"/>
-        <item x="192"/>
-        <item x="390"/>
-        <item x="389"/>
-        <item x="106"/>
-        <item x="287"/>
-        <item x="197"/>
-        <item x="302"/>
-        <item x="404"/>
-        <item x="54"/>
-        <item x="381"/>
-        <item x="246"/>
-        <item x="41"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="201"/>
-        <item x="22"/>
-        <item x="8"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="265"/>
-        <item x="86"/>
-        <item x="345"/>
-        <item x="63"/>
-        <item x="91"/>
-        <item x="39"/>
-        <item x="93"/>
-        <item x="270"/>
-        <item x="229"/>
-        <item x="161"/>
-        <item x="387"/>
-        <item x="149"/>
-        <item x="231"/>
-        <item x="23"/>
-        <item x="15"/>
-        <item x="209"/>
-        <item x="31"/>
-        <item x="139"/>
-        <item x="56"/>
-        <item x="7"/>
-        <item x="369"/>
-        <item x="109"/>
-        <item x="253"/>
-        <item x="396"/>
-        <item x="375"/>
-        <item x="119"/>
-        <item x="303"/>
-        <item x="71"/>
-        <item x="403"/>
-        <item x="312"/>
-        <item x="247"/>
-        <item x="112"/>
-        <item x="136"/>
-        <item x="64"/>
-        <item x="60"/>
-        <item x="374"/>
-        <item x="340"/>
-        <item x="288"/>
-        <item x="326"/>
-        <item x="130"/>
-        <item x="339"/>
-        <item x="293"/>
-        <item x="45"/>
-        <item x="276"/>
-        <item x="323"/>
-        <item x="271"/>
-        <item x="311"/>
-        <item x="0"/>
-        <item x="310"/>
-        <item x="322"/>
-        <item x="337"/>
-        <item x="72"/>
-        <item x="128"/>
-        <item x="157"/>
-        <item x="363"/>
-        <item x="18"/>
-        <item x="154"/>
-        <item x="249"/>
-        <item x="155"/>
-        <item x="75"/>
-        <item x="138"/>
-        <item x="260"/>
-        <item x="205"/>
-        <item x="299"/>
-        <item x="94"/>
-        <item x="277"/>
-        <item x="321"/>
-        <item x="49"/>
-        <item x="26"/>
-        <item x="274"/>
-        <item x="306"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Gender" fld="3" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2A75BE5-3A20-4653-8B73-8C85146E8AE7}" name="7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="G15:H57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField numFmtId="1" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField numFmtId="1" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField numFmtId="14" showAll="0" defaultSubtotal="0">
-      <items count="405">
-        <item x="2"/>
-        <item x="132"/>
-        <item x="166"/>
-        <item x="189"/>
-        <item x="307"/>
-        <item x="44"/>
-        <item x="234"/>
-        <item x="360"/>
-        <item x="145"/>
-        <item x="289"/>
-        <item x="258"/>
-        <item x="380"/>
-        <item x="74"/>
-        <item x="334"/>
-        <item x="213"/>
-        <item x="382"/>
-        <item x="255"/>
-        <item x="142"/>
-        <item x="232"/>
-        <item x="92"/>
-        <item x="14"/>
-        <item x="46"/>
-        <item x="353"/>
-        <item x="243"/>
-        <item x="67"/>
-        <item x="85"/>
-        <item x="84"/>
-        <item x="203"/>
-        <item x="208"/>
-        <item x="314"/>
-        <item x="17"/>
-        <item x="309"/>
-        <item x="272"/>
-        <item x="199"/>
-        <item x="349"/>
-        <item x="183"/>
-        <item x="96"/>
-        <item x="393"/>
-        <item x="346"/>
-        <item x="372"/>
-        <item x="268"/>
-        <item x="212"/>
-        <item x="111"/>
-        <item x="230"/>
-        <item x="221"/>
-        <item x="206"/>
-        <item x="336"/>
-        <item x="202"/>
-        <item x="269"/>
-        <item x="388"/>
-        <item x="238"/>
-        <item x="53"/>
-        <item x="254"/>
-        <item x="316"/>
-        <item x="319"/>
-        <item x="220"/>
-        <item x="200"/>
-        <item x="159"/>
-        <item x="216"/>
-        <item x="117"/>
-        <item x="352"/>
-        <item x="315"/>
-        <item x="292"/>
-        <item x="156"/>
-        <item x="261"/>
-        <item x="190"/>
-        <item x="113"/>
-        <item x="280"/>
-        <item x="146"/>
-        <item x="150"/>
-        <item x="172"/>
-        <item x="12"/>
-        <item x="19"/>
-        <item x="366"/>
-        <item x="262"/>
-        <item x="223"/>
-        <item x="52"/>
-        <item x="347"/>
-        <item x="81"/>
-        <item x="68"/>
-        <item x="402"/>
-        <item x="37"/>
-        <item x="305"/>
-        <item x="36"/>
-        <item x="395"/>
-        <item x="368"/>
-        <item x="77"/>
-        <item x="98"/>
-        <item x="171"/>
-        <item x="135"/>
-        <item x="400"/>
-        <item x="267"/>
-        <item x="217"/>
-        <item x="110"/>
-        <item x="134"/>
-        <item x="196"/>
-        <item x="298"/>
-        <item x="335"/>
-        <item x="185"/>
-        <item x="373"/>
-        <item x="55"/>
-        <item x="103"/>
-        <item x="351"/>
-        <item x="28"/>
-        <item x="50"/>
-        <item x="359"/>
-        <item x="327"/>
-        <item x="153"/>
-        <item x="181"/>
-        <item x="286"/>
-        <item x="401"/>
-        <item x="123"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="182"/>
-        <item x="204"/>
-        <item x="80"/>
-        <item x="4"/>
-        <item x="69"/>
-        <item x="143"/>
-        <item x="279"/>
-        <item x="186"/>
-        <item x="364"/>
-        <item x="301"/>
-        <item x="376"/>
-        <item x="342"/>
-        <item x="195"/>
-        <item x="148"/>
-        <item x="10"/>
-        <item x="320"/>
-        <item x="83"/>
-        <item x="235"/>
-        <item x="79"/>
-        <item x="251"/>
-        <item x="394"/>
-        <item x="332"/>
-        <item x="137"/>
-        <item x="259"/>
-        <item x="118"/>
-        <item x="99"/>
-        <item x="141"/>
-        <item x="188"/>
-        <item x="101"/>
-        <item x="398"/>
-        <item x="392"/>
-        <item x="356"/>
-        <item x="58"/>
-        <item x="180"/>
-        <item x="82"/>
-        <item x="211"/>
-        <item x="282"/>
-        <item x="3"/>
-        <item x="275"/>
-        <item x="225"/>
-        <item x="252"/>
-        <item x="355"/>
-        <item x="297"/>
-        <item x="283"/>
-        <item x="27"/>
-        <item x="354"/>
-        <item x="90"/>
-        <item x="371"/>
-        <item x="384"/>
-        <item x="168"/>
-        <item x="66"/>
-        <item x="341"/>
-        <item x="362"/>
-        <item x="129"/>
-        <item x="30"/>
-        <item x="294"/>
-        <item x="6"/>
-        <item x="115"/>
-        <item x="218"/>
-        <item x="105"/>
-        <item x="163"/>
-        <item x="224"/>
-        <item x="125"/>
-        <item x="328"/>
-        <item x="207"/>
-        <item x="120"/>
-        <item x="397"/>
-        <item x="21"/>
-        <item x="264"/>
-        <item x="333"/>
-        <item x="236"/>
-        <item x="300"/>
-        <item x="198"/>
-        <item x="226"/>
-        <item x="348"/>
-        <item x="383"/>
-        <item x="324"/>
-        <item x="385"/>
-        <item x="290"/>
-        <item x="144"/>
-        <item x="121"/>
-        <item x="62"/>
-        <item x="140"/>
-        <item x="215"/>
-        <item x="367"/>
-        <item x="122"/>
-        <item x="219"/>
-        <item x="178"/>
-        <item x="170"/>
-        <item x="13"/>
-        <item x="47"/>
-        <item x="194"/>
-        <item x="152"/>
-        <item x="95"/>
-        <item x="187"/>
-        <item x="158"/>
-        <item x="248"/>
-        <item x="242"/>
-        <item x="184"/>
-        <item x="296"/>
-        <item x="127"/>
-        <item x="114"/>
-        <item x="116"/>
-        <item x="237"/>
-        <item x="399"/>
-        <item x="29"/>
-        <item x="278"/>
-        <item x="131"/>
-        <item x="124"/>
-        <item x="357"/>
-        <item x="245"/>
-        <item x="228"/>
-        <item x="97"/>
-        <item x="100"/>
-        <item x="89"/>
-        <item x="227"/>
-        <item x="5"/>
-        <item x="263"/>
-        <item x="108"/>
-        <item x="358"/>
-        <item x="210"/>
-        <item x="239"/>
-        <item x="281"/>
-        <item x="175"/>
-        <item x="193"/>
-        <item x="179"/>
-        <item x="361"/>
-        <item x="51"/>
-        <item x="1"/>
-        <item x="317"/>
-        <item x="266"/>
-        <item x="65"/>
-        <item x="391"/>
-        <item x="40"/>
-        <item x="244"/>
-        <item x="160"/>
-        <item x="162"/>
-        <item x="291"/>
-        <item x="191"/>
-        <item x="173"/>
-        <item x="133"/>
-        <item x="256"/>
-        <item x="88"/>
-        <item x="370"/>
-        <item x="102"/>
-        <item x="330"/>
-        <item x="365"/>
-        <item x="35"/>
-        <item x="164"/>
-        <item x="284"/>
-        <item x="107"/>
-        <item x="318"/>
-        <item x="24"/>
-        <item x="48"/>
-        <item x="165"/>
-        <item x="176"/>
-        <item x="344"/>
-        <item x="240"/>
-        <item x="379"/>
-        <item x="304"/>
-        <item x="151"/>
-        <item x="313"/>
-        <item x="295"/>
-        <item x="273"/>
-        <item x="233"/>
-        <item x="42"/>
-        <item x="87"/>
-        <item x="308"/>
-        <item x="16"/>
-        <item x="126"/>
-        <item x="70"/>
-        <item x="285"/>
-        <item x="350"/>
-        <item x="73"/>
-        <item x="250"/>
-        <item x="257"/>
-        <item x="343"/>
-        <item x="329"/>
-        <item x="177"/>
-        <item x="33"/>
-        <item x="78"/>
-        <item x="34"/>
-        <item x="38"/>
-        <item x="61"/>
-        <item x="147"/>
-        <item x="169"/>
-        <item x="104"/>
-        <item x="325"/>
-        <item x="241"/>
-        <item x="386"/>
-        <item x="43"/>
-        <item x="214"/>
-        <item x="25"/>
-        <item x="174"/>
-        <item x="338"/>
-        <item x="167"/>
-        <item x="59"/>
-        <item x="222"/>
-        <item x="331"/>
-        <item x="76"/>
-        <item x="11"/>
-        <item x="192"/>
-        <item x="390"/>
-        <item x="389"/>
-        <item x="106"/>
-        <item x="287"/>
-        <item x="197"/>
-        <item x="302"/>
-        <item x="404"/>
-        <item x="54"/>
-        <item x="381"/>
-        <item x="246"/>
-        <item x="41"/>
-        <item x="20"/>
-        <item x="32"/>
-        <item x="201"/>
-        <item x="22"/>
-        <item x="8"/>
-        <item x="57"/>
-        <item x="9"/>
-        <item x="265"/>
-        <item x="86"/>
-        <item x="345"/>
-        <item x="63"/>
-        <item x="91"/>
-        <item x="39"/>
-        <item x="93"/>
-        <item x="270"/>
-        <item x="229"/>
-        <item x="161"/>
-        <item x="387"/>
-        <item x="149"/>
-        <item x="231"/>
-        <item x="23"/>
-        <item x="15"/>
-        <item x="209"/>
-        <item x="31"/>
-        <item x="139"/>
-        <item x="56"/>
-        <item x="7"/>
-        <item x="369"/>
-        <item x="109"/>
-        <item x="253"/>
-        <item x="396"/>
-        <item x="375"/>
-        <item x="119"/>
-        <item x="303"/>
-        <item x="71"/>
-        <item x="403"/>
-        <item x="312"/>
-        <item x="247"/>
-        <item x="112"/>
-        <item x="136"/>
-        <item x="64"/>
-        <item x="60"/>
-        <item x="374"/>
-        <item x="340"/>
-        <item x="288"/>
-        <item x="326"/>
-        <item x="130"/>
-        <item x="339"/>
-        <item x="293"/>
-        <item x="45"/>
-        <item x="276"/>
-        <item x="323"/>
-        <item x="271"/>
-        <item x="311"/>
-        <item x="0"/>
-        <item x="310"/>
-        <item x="322"/>
-        <item x="337"/>
-        <item x="72"/>
-        <item x="128"/>
-        <item x="157"/>
-        <item x="363"/>
-        <item x="18"/>
-        <item x="154"/>
-        <item x="249"/>
-        <item x="155"/>
-        <item x="75"/>
-        <item x="138"/>
-        <item x="260"/>
-        <item x="205"/>
-        <item x="299"/>
-        <item x="94"/>
-        <item x="277"/>
-        <item x="321"/>
-        <item x="49"/>
-        <item x="26"/>
-        <item x="274"/>
-        <item x="306"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="164" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="10"/>
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="42">
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Purchase_Amount" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -25978,24 +25981,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
-        <v>1328</v>
+      <c r="A1" s="47" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="39"/>
     </row>
-    <row r="3" spans="1:2" ht="63" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
-        <v>1329</v>
+    <row r="3" spans="1:2" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="46" t="s">
+        <v>1365</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="39"/>
     </row>
     <row r="5" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="48" t="s">
-        <v>1330</v>
+      <c r="A5" s="47" t="s">
+        <v>1327</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -26003,27 +26006,27 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>1336</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -26031,55 +26034,55 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="39"/>
     </row>
     <row r="15" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="48" t="s">
-        <v>1331</v>
+      <c r="A15" s="47" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
-        <v>1369</v>
+      <c r="A16" s="49" t="s">
+        <v>1358</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="51" t="s">
-        <v>1370</v>
+      <c r="B17" s="50" t="s">
+        <v>1359</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -26091,6 +26094,121 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0EF89C-EA03-4502-AD1D-D7325C3719C2}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I518"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -41000,121 +41118,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0EF89C-EA03-4502-AD1D-D7325C3719C2}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -55240,7 +55243,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
@@ -55251,7 +55254,7 @@
         <v>1280</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55259,7 +55262,7 @@
         <v>1281</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55276,7 +55279,7 @@
         <v>1283</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="90" x14ac:dyDescent="0.25">
@@ -55284,7 +55287,7 @@
         <v>1284</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1295</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55292,7 +55295,7 @@
         <v>1285</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="90" x14ac:dyDescent="0.25">
@@ -55300,7 +55303,7 @@
         <v>1286</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55308,7 +55311,7 @@
         <v>1287</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55325,7 +55328,7 @@
         <v>1289</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55363,19 +55366,19 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B1" s="53"/>
       <c r="D1" s="53" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E1" s="53"/>
       <c r="G1" s="53" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H1" s="53"/>
       <c r="J1" s="53" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="K1" s="53"/>
     </row>
@@ -55384,7 +55387,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>4</v>
@@ -55402,7 +55405,7 @@
         <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -55589,15 +55592,15 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="53" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B13" s="53"/>
       <c r="D13" s="53" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E13" s="53"/>
       <c r="G13" s="53" t="s">
-        <v>1326</v>
+        <v>1360</v>
       </c>
       <c r="H13" s="54"/>
     </row>
@@ -55606,7 +55609,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>4</v>
@@ -55615,7 +55618,7 @@
         <v>1293</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H15" t="s">
         <v>1293</v>
@@ -55635,7 +55638,7 @@
         <v>774776</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H16" s="20"/>
     </row>
@@ -55653,7 +55656,7 @@
         <v>786394</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H17" s="20">
         <v>58409</v>
@@ -55673,7 +55676,7 @@
         <v>727703</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H18" s="20">
         <v>136181</v>
@@ -55687,7 +55690,7 @@
         <v>725526</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H19" s="20">
         <v>162399</v>
@@ -55701,7 +55704,7 @@
         <v>901880</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H20" s="20">
         <v>221028</v>
@@ -55715,7 +55718,7 @@
         <v>870348</v>
       </c>
       <c r="G21" s="31" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H21" s="20">
         <v>103264</v>
@@ -55729,7 +55732,7 @@
         <v>4786627</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H22" s="20">
         <v>119071</v>
@@ -55737,7 +55740,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G23" s="31" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H23" s="20">
         <v>228794</v>
@@ -55745,7 +55748,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G24" s="31" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H24" s="20">
         <v>95775</v>
@@ -55753,13 +55756,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G25" s="23" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H25" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G26" s="31" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H26" s="20">
         <v>167196</v>
@@ -55767,7 +55770,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G27" s="31" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H27" s="20">
         <v>93298</v>
@@ -55775,7 +55778,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G28" s="31" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H28" s="20">
         <v>114123</v>
@@ -55783,7 +55786,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G29" s="31" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H29" s="20">
         <v>140912</v>
@@ -55791,7 +55794,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G30" s="31" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H30" s="20">
         <v>109714</v>
@@ -55799,7 +55802,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G31" s="31" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H31" s="20">
         <v>100646</v>
@@ -55807,7 +55810,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G32" s="31" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H32" s="20">
         <v>121438</v>
@@ -55815,7 +55818,7 @@
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G33" s="31" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H33" s="20">
         <v>165309</v>
@@ -55823,7 +55826,7 @@
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G34" s="31" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H34" s="20">
         <v>117942</v>
@@ -55831,7 +55834,7 @@
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G35" s="31" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H35" s="20">
         <v>147154</v>
@@ -55839,7 +55842,7 @@
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G36" s="31" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H36" s="20">
         <v>136068</v>
@@ -55847,7 +55850,7 @@
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G37" s="31" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H37" s="20">
         <v>111485</v>
@@ -55855,13 +55858,13 @@
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G38" s="23" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H38" s="20"/>
     </row>
     <row r="39" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G39" s="31" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H39" s="20">
         <v>108636</v>
@@ -55869,7 +55872,7 @@
     </row>
     <row r="40" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G40" s="31" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H40" s="20">
         <v>165667</v>
@@ -55877,7 +55880,7 @@
     </row>
     <row r="41" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G41" s="31" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H41" s="20">
         <v>154856</v>
@@ -55885,7 +55888,7 @@
     </row>
     <row r="42" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G42" s="31" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H42" s="20">
         <v>130052</v>
@@ -55893,7 +55896,7 @@
     </row>
     <row r="43" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G43" s="31" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H43" s="20">
         <v>85570</v>
@@ -55901,7 +55904,7 @@
     </row>
     <row r="44" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G44" s="31" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H44" s="20">
         <v>188033</v>
@@ -55909,7 +55912,7 @@
     </row>
     <row r="45" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G45" s="31" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H45" s="20">
         <v>174290</v>
@@ -55917,7 +55920,7 @@
     </row>
     <row r="46" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G46" s="31" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H46" s="20">
         <v>146085</v>
@@ -55925,7 +55928,7 @@
     </row>
     <row r="47" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G47" s="31" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H47" s="20">
         <v>89291</v>
@@ -55933,7 +55936,7 @@
     </row>
     <row r="48" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G48" s="31" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H48" s="20">
         <v>79985</v>
@@ -55941,7 +55944,7 @@
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G49" s="31" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H49" s="20">
         <v>83427</v>
@@ -55949,7 +55952,7 @@
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G50" s="31" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H50" s="20">
         <v>112986</v>
@@ -55957,13 +55960,13 @@
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G51" s="23" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H51" s="20"/>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G52" s="31" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H52" s="20">
         <v>176692</v>
@@ -55971,7 +55974,7 @@
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G53" s="31" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H53" s="20">
         <v>103366</v>
@@ -55979,7 +55982,7 @@
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G54" s="31" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H54" s="20">
         <v>110988</v>
@@ -55987,7 +55990,7 @@
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G55" s="31" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H55" s="20">
         <v>146527</v>
@@ -55995,7 +55998,7 @@
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G56" s="31" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H56" s="20">
         <v>79970</v>
@@ -56121,27 +56124,27 @@
     </row>
     <row r="4" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="36" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="49" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="36" t="s">
-        <v>1367</v>
+      <c r="B6" s="48" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="27" x14ac:dyDescent="0.25">
+      <c r="B7" s="48" t="s">
+        <v>1370</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="36" t="s">
-        <v>1368</v>
+      <c r="B8" s="48" t="s">
+        <v>1361</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
